--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127457185</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>130098022</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -675,53 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127457185</v>
+        <v>130098022</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -760,12 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,37 +786,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130098022</v>
+        <v>127457185</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -862,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33898-2022 artfynd.xlsx
+++ b/artfynd/A 33898-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,8 +911,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127457185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>